--- a/modelos_importacao/Modelo_Importacao_Contactos.xlsx
+++ b/modelos_importacao/Modelo_Importacao_Contactos.xlsx
@@ -399,16 +399,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
     <col min="9" max="9" width="32.83203125" customWidth="1"/>
-    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="10" max="10" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
